--- a/logs/logic_grid_puzzle/o1-mini_wo_sys_mes/accuracy_results_o1-mini_wo_sys_mes.xlsx
+++ b/logs/logic_grid_puzzle/o1-mini_wo_sys_mes/accuracy_results_o1-mini_wo_sys_mes.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1010,7 +1010,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1723,7 +1723,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1838,7 +1838,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2114,7 +2114,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2229,7 +2229,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2298,7 +2298,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2436,7 +2436,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2482,7 +2482,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2574,7 +2574,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2597,7 +2597,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2620,7 +2620,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2689,7 +2689,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2804,7 +2804,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2827,7 +2827,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2896,7 +2896,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2965,7 +2965,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2988,7 +2988,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3057,7 +3057,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3080,7 +3080,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3103,7 +3103,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3172,7 +3172,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3287,7 +3287,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3333,7 +3333,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3448,7 +3448,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3471,7 +3471,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3586,7 +3586,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3609,7 +3609,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3655,7 +3655,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3678,7 +3678,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3701,7 +3701,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3724,7 +3724,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3770,7 +3770,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3793,7 +3793,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3816,7 +3816,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3839,7 +3839,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3908,7 +3908,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3954,7 +3954,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3977,7 +3977,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4000,7 +4000,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4023,7 +4023,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4069,7 +4069,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4092,7 +4092,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4138,7 +4138,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4161,7 +4161,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4184,7 +4184,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4230,7 +4230,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4299,7 +4299,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4345,7 +4345,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4391,7 +4391,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4460,7 +4460,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4483,7 +4483,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4506,7 +4506,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4529,7 +4529,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4575,7 +4575,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4690,7 +4690,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4736,7 +4736,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4782,7 +4782,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4851,7 +4851,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4897,7 +4897,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4920,7 +4920,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5012,7 +5012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5035,7 +5035,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5106,7 +5106,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5175,7 +5175,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5244,7 +5244,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5267,7 +5267,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5290,7 +5290,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5336,7 +5336,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5359,7 +5359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5382,7 +5382,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5405,7 +5405,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5428,7 +5428,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5474,7 +5474,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5520,7 +5520,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5543,7 +5543,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5566,7 +5566,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5612,7 +5612,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5635,7 +5635,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5681,7 +5681,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5704,7 +5704,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5727,7 +5727,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5750,7 +5750,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5865,7 +5865,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5888,7 +5888,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5911,7 +5911,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5934,7 +5934,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5957,7 +5957,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5980,7 +5980,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6003,7 +6003,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6026,7 +6026,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6049,7 +6049,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6072,7 +6072,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6118,7 +6118,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6141,7 +6141,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6187,7 +6187,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6279,7 +6279,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6325,7 +6325,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6371,7 +6371,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6394,7 +6394,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6417,7 +6417,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6440,7 +6440,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6486,7 +6486,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6509,7 +6509,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6532,7 +6532,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6555,7 +6555,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6578,7 +6578,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6601,7 +6601,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6624,7 +6624,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6670,7 +6670,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6693,7 +6693,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6716,7 +6716,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6762,7 +6762,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6785,7 +6785,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6808,7 +6808,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6831,7 +6831,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6854,7 +6854,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6877,7 +6877,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6900,7 +6900,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6923,7 +6923,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6946,7 +6946,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6992,7 +6992,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7015,7 +7015,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7038,7 +7038,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7061,7 +7061,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7084,7 +7084,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7107,7 +7107,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7153,7 +7153,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7176,7 +7176,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7199,7 +7199,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7222,7 +7222,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7245,7 +7245,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7268,7 +7268,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7291,7 +7291,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7314,7 +7314,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7337,7 +7337,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7383,7 +7383,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7406,7 +7406,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7429,7 +7429,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7452,7 +7452,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7498,7 +7498,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7544,7 +7544,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7567,7 +7567,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7590,7 +7590,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7613,7 +7613,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7636,7 +7636,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7682,7 +7682,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7705,7 +7705,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7751,7 +7751,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7774,7 +7774,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7797,7 +7797,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7820,7 +7820,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7843,7 +7843,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7912,7 +7912,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7935,7 +7935,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7958,7 +7958,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7981,7 +7981,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -8004,7 +8004,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -8027,7 +8027,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -8050,7 +8050,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8073,7 +8073,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -8119,7 +8119,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8142,7 +8142,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8165,7 +8165,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -8188,7 +8188,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8211,7 +8211,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8234,7 +8234,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8280,7 +8280,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8349,7 +8349,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -8372,7 +8372,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -8395,7 +8395,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -8418,7 +8418,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8441,7 +8441,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8464,7 +8464,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8510,7 +8510,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8533,7 +8533,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8556,7 +8556,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8579,7 +8579,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8602,7 +8602,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8671,7 +8671,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8694,7 +8694,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8717,7 +8717,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8740,7 +8740,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8763,7 +8763,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8786,7 +8786,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8809,7 +8809,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8832,7 +8832,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8855,7 +8855,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8878,7 +8878,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8901,7 +8901,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8924,7 +8924,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -8947,7 +8947,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8970,7 +8970,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8993,7 +8993,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -9016,7 +9016,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -9108,7 +9108,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -9131,7 +9131,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -9154,7 +9154,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -9177,7 +9177,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -9200,7 +9200,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -9223,7 +9223,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -9246,7 +9246,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -9269,7 +9269,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -9292,7 +9292,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -9315,7 +9315,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -9338,7 +9338,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -9384,7 +9384,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -9407,7 +9407,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -9453,7 +9453,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -9476,7 +9476,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -9499,7 +9499,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -9522,7 +9522,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -9545,7 +9545,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -9568,7 +9568,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -9591,7 +9591,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -9614,7 +9614,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -9637,7 +9637,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -9660,7 +9660,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -9683,7 +9683,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -9708,7 +9708,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -9731,7 +9731,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -9754,7 +9754,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -9777,7 +9777,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -9800,7 +9800,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -9823,7 +9823,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -9869,7 +9869,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -9892,7 +9892,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -9915,7 +9915,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -9938,7 +9938,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -9961,7 +9961,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -9984,7 +9984,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -10007,7 +10007,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -10030,7 +10030,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -10053,7 +10053,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10099,7 +10099,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10122,7 +10122,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -10145,7 +10145,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -10168,7 +10168,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -10214,7 +10214,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -10237,7 +10237,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -10260,7 +10260,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -10283,7 +10283,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -10306,7 +10306,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -10329,7 +10329,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -10352,7 +10352,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -10375,7 +10375,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -10398,7 +10398,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -10421,7 +10421,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -10444,7 +10444,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -10513,7 +10513,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -10536,7 +10536,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -10582,7 +10582,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -10605,7 +10605,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -10628,7 +10628,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -10651,7 +10651,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -10674,7 +10674,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -10720,7 +10720,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -10743,7 +10743,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -10766,7 +10766,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -10789,7 +10789,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -10812,7 +10812,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -10835,7 +10835,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -10881,7 +10881,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -10904,7 +10904,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -10927,7 +10927,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -10950,7 +10950,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -10973,7 +10973,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -10996,7 +10996,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -11019,7 +11019,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -11042,7 +11042,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -11065,7 +11065,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -11088,7 +11088,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -11111,7 +11111,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -11134,7 +11134,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -11157,7 +11157,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -11180,7 +11180,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -11203,7 +11203,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -11226,7 +11226,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -11272,7 +11272,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -11295,7 +11295,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -11318,7 +11318,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -11364,7 +11364,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -11387,7 +11387,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -11410,7 +11410,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -11433,7 +11433,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -11479,7 +11479,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -11502,7 +11502,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -11525,7 +11525,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -11548,7 +11548,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -11571,7 +11571,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -11594,7 +11594,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -11617,7 +11617,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -11663,7 +11663,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -11686,7 +11686,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -11709,7 +11709,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -11732,7 +11732,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -11755,7 +11755,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -11778,7 +11778,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -11801,7 +11801,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -11824,7 +11824,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -11847,7 +11847,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -11870,7 +11870,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -11893,7 +11893,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -11916,7 +11916,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -11939,7 +11939,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -11985,7 +11985,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -12008,7 +12008,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -12054,7 +12054,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -12077,7 +12077,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -12100,7 +12100,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -12123,7 +12123,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -12146,7 +12146,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -12169,7 +12169,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -12192,7 +12192,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -12215,7 +12215,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -12238,7 +12238,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -12261,7 +12261,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -12284,7 +12284,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -12307,7 +12307,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -12330,7 +12330,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -12353,7 +12353,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -12376,7 +12376,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -12399,7 +12399,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -12445,7 +12445,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -12468,7 +12468,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -12491,7 +12491,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -12514,7 +12514,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -12537,7 +12537,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -12560,7 +12560,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -12583,7 +12583,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -12606,7 +12606,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -12629,7 +12629,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -12652,7 +12652,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -12675,7 +12675,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -12698,7 +12698,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -12721,7 +12721,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -12767,7 +12767,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -12790,7 +12790,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -12813,7 +12813,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -12836,7 +12836,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -12859,7 +12859,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -12882,7 +12882,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -12905,7 +12905,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -12928,7 +12928,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -12951,7 +12951,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -12974,7 +12974,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -12997,7 +12997,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -13020,7 +13020,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -13043,7 +13043,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -13066,7 +13066,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -13089,7 +13089,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -13112,7 +13112,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -13135,7 +13135,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -13158,7 +13158,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -13181,7 +13181,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -13204,7 +13204,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -13227,7 +13227,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -13250,7 +13250,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -13273,7 +13273,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -13296,7 +13296,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -13319,7 +13319,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -13342,7 +13342,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -13365,7 +13365,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -13434,7 +13434,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -13457,7 +13457,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -13480,7 +13480,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -13503,7 +13503,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -13572,7 +13572,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -13595,7 +13595,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -13618,7 +13618,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -13641,7 +13641,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -13664,7 +13664,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -13687,7 +13687,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -13710,7 +13710,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -13733,7 +13733,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -13756,7 +13756,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -13779,7 +13779,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -13802,7 +13802,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -13825,7 +13825,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -13848,7 +13848,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -13871,7 +13871,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -13917,7 +13917,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -13940,7 +13940,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -13963,7 +13963,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -13986,7 +13986,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -14009,7 +14009,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -14032,7 +14032,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -14055,7 +14055,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -14078,7 +14078,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -14101,7 +14101,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -14124,7 +14124,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -14147,7 +14147,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -14193,7 +14193,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -14216,7 +14216,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -14239,7 +14239,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -14262,7 +14262,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -14285,7 +14285,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -14308,7 +14308,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200__wo_sys.jsonl</t>
+          <t>logic_grid_puzzle_200.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end200_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
